--- a/results_minsup_ESBL/minsup_0_001/rep8/describ_graphs_0.95.xlsx
+++ b/results_minsup_ESBL/minsup_0_001/rep8/describ_graphs_0.95.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t xml:space="preserve">dataset</t>
   </si>
@@ -24,6 +24,15 @@
   </si>
   <si>
     <t xml:space="preserve">2018_BLSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019_BLSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020_BLSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021_BLSE</t>
   </si>
   <si>
     <t xml:space="preserve">2022_BLSE</t>
@@ -382,9 +391,42 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
+        <v>12.7692307692308</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.510769230769231</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="n">
+        <v>13</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="n">
+        <v>12.6923076923077</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.507692307692308</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="n">
         <v>12.8461538461538</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C6" t="n">
         <v>0.513846153846154</v>
       </c>
     </row>
